--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_6.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02257869114259973</v>
+        <v>0.01711495292561468</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008439159269661285</v>
+        <v>0.008432782635230575</v>
       </c>
       <c r="C2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>26517392</v>
+        <v>4267041</v>
       </c>
       <c r="L2" t="n">
-        <v>14776055</v>
+        <v>2167546</v>
       </c>
       <c r="M2" t="n">
-        <v>3619292</v>
+        <v>492977</v>
       </c>
       <c r="N2" t="n">
-        <v>168698</v>
+        <v>13633</v>
       </c>
       <c r="O2" t="n">
-        <v>2196365</v>
+        <v>294330</v>
       </c>
       <c r="P2" t="n">
-        <v>875744</v>
+        <v>114927</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999750256538391</v>
+        <v>0.9999253749847412</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8729146122932434</v>
+        <v>0.8205958604812622</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7491480708122253</v>
+        <v>0.6685636043548584</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6810297966003418</v>
+        <v>0.5727402567863464</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3636665344238281</v>
+        <v>0.1413244009017944</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7347626686096191</v>
+        <v>0.6325610280036926</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8181044459342957</v>
+        <v>0.7579537034034729</v>
       </c>
       <c r="X2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28768914</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17794252</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4795649</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353654</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2754762</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564045071601868</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113450646400452</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582964539527893</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622424125671387</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020413160324097</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005601374769273222</v>
+        <v>0.004141111879248769</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002024109024678931</v>
+        <v>0.002022202495942296</v>
       </c>
       <c r="C3" t="n">
-        <v>699</v>
+        <v>331</v>
       </c>
       <c r="D3" t="n">
-        <v>26517392</v>
+        <v>4267041</v>
       </c>
       <c r="E3" t="n">
-        <v>3430995</v>
+        <v>721996</v>
       </c>
       <c r="F3" t="n">
-        <v>82016</v>
+        <v>17899</v>
       </c>
       <c r="G3" t="n">
-        <v>8154</v>
+        <v>1298</v>
       </c>
       <c r="H3" t="n">
-        <v>4759</v>
+        <v>1018</v>
       </c>
       <c r="I3" t="n">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>59939795</v>
+        <v>10016151</v>
       </c>
       <c r="K3" t="n">
-        <v>63813589</v>
+        <v>10387103</v>
       </c>
       <c r="L3" t="n">
-        <v>73216162</v>
+        <v>11975794</v>
       </c>
       <c r="M3" t="n">
-        <v>90431097</v>
+        <v>15026810</v>
       </c>
       <c r="N3" t="n">
-        <v>96888763</v>
+        <v>16157423</v>
       </c>
       <c r="O3" t="n">
-        <v>93870138</v>
+        <v>15648692</v>
       </c>
       <c r="P3" t="n">
-        <v>96363664</v>
+        <v>16099459</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8826123476028442</v>
+        <v>0.8517714142799377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7556352019309998</v>
+        <v>0.6609867215156555</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6472088098526001</v>
+        <v>0.5272295475006104</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3156454861164093</v>
+        <v>0.1525899916887283</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7188445925712585</v>
+        <v>0.5771867036819458</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7549354434013367</v>
+        <v>0.5941222310066223</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28768914</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1183340</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>50881</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40695</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>202</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>59940738</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66362824</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76432907</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91334490</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97003575</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94363832</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96478850</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575526118278503</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099832773208618</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575672507286072</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6617108583450317</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016014337539673</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05745526385308643</v>
+        <v>0.04630480783999353</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03193431931948926</v>
+        <v>0.03191410809705398</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>3639472</v>
+        <v>877253</v>
       </c>
       <c r="E4" t="n">
-        <v>14776055</v>
+        <v>2167546</v>
       </c>
       <c r="F4" t="n">
-        <v>1002362</v>
+        <v>203363</v>
       </c>
       <c r="G4" t="n">
-        <v>40388</v>
+        <v>9590</v>
       </c>
       <c r="H4" t="n">
-        <v>88189</v>
+        <v>19660</v>
       </c>
       <c r="I4" t="n">
-        <v>7966</v>
+        <v>1802</v>
       </c>
       <c r="J4" t="n">
-        <v>943</v>
+        <v>471</v>
       </c>
       <c r="K4" t="n">
-        <v>3860599</v>
+        <v>932889</v>
       </c>
       <c r="L4" t="n">
-        <v>4947756</v>
+        <v>1074548</v>
       </c>
       <c r="M4" t="n">
-        <v>1695148</v>
+        <v>367757</v>
       </c>
       <c r="N4" t="n">
-        <v>295183</v>
+        <v>82833</v>
       </c>
       <c r="O4" t="n">
-        <v>792852</v>
+        <v>170969</v>
       </c>
       <c r="P4" t="n">
-        <v>194711</v>
+        <v>36701</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999875426292419</v>
+        <v>0.9999626874923706</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8777366876602173</v>
+        <v>0.8358930349349976</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7523776292800903</v>
+        <v>0.6647536158561707</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6636887192726135</v>
+        <v>0.5490434169769287</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3379587233066559</v>
+        <v>0.1467413008213043</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7267164587974548</v>
+        <v>0.6036064624786377</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7852516174316406</v>
+        <v>0.6661121845245361</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1224375</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17794252</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>495701</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32906</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6840</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1311364</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1731011</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>791755</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180371</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299158</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569782018661499</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106636047363281</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579316735267639</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619765162467957</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213152885437</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>146254</v>
+        <v>38424</v>
       </c>
       <c r="E5" t="n">
-        <v>1286302</v>
+        <v>295964</v>
       </c>
       <c r="F5" t="n">
-        <v>3619292</v>
+        <v>492977</v>
       </c>
       <c r="G5" t="n">
-        <v>113437</v>
+        <v>26546</v>
       </c>
       <c r="H5" t="n">
-        <v>392638</v>
+        <v>73326</v>
       </c>
       <c r="I5" t="n">
-        <v>34200</v>
+        <v>7779</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3526820</v>
+        <v>742567</v>
       </c>
       <c r="L5" t="n">
-        <v>4778427</v>
+        <v>1111712</v>
       </c>
       <c r="M5" t="n">
-        <v>1972863</v>
+        <v>442056</v>
       </c>
       <c r="N5" t="n">
-        <v>365756</v>
+        <v>75711</v>
       </c>
       <c r="O5" t="n">
-        <v>859045</v>
+        <v>215609</v>
       </c>
       <c r="P5" t="n">
-        <v>284281</v>
+        <v>78513</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999903440475464</v>
+        <v>0.9999711513519287</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9244009256362915</v>
+        <v>0.8973976373672485</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9004672169685364</v>
+        <v>0.8661167621612549</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9624634385108948</v>
+        <v>0.9504082798957825</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9932363033294678</v>
+        <v>0.9902909994125366</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9830953478813171</v>
+        <v>0.9763265252113342</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9950982332229614</v>
+        <v>0.9929444789886475</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>47971</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510291</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4795649</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59673</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174773</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1275298</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1760230</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>796506</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>180800</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300648</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735293984413147</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642724394798279</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837465286254883</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963039755821228</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938619136810303</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983705282211304</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>70046</v>
+        <v>15805</v>
       </c>
       <c r="E6" t="n">
-        <v>104507</v>
+        <v>20352</v>
       </c>
       <c r="F6" t="n">
-        <v>121685</v>
+        <v>27956</v>
       </c>
       <c r="G6" t="n">
-        <v>168698</v>
+        <v>13633</v>
       </c>
       <c r="H6" t="n">
-        <v>63232</v>
+        <v>10520</v>
       </c>
       <c r="I6" t="n">
-        <v>6234</v>
+        <v>1063</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38703</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32037</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65304</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353654</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41870</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>4631</v>
+        <v>1361</v>
       </c>
       <c r="E7" t="n">
-        <v>118037</v>
+        <v>34034</v>
       </c>
       <c r="F7" t="n">
-        <v>466077</v>
+        <v>111870</v>
       </c>
       <c r="G7" t="n">
-        <v>124140</v>
+        <v>42269</v>
       </c>
       <c r="H7" t="n">
-        <v>2196365</v>
+        <v>294330</v>
       </c>
       <c r="I7" t="n">
-        <v>146114</v>
+        <v>26032</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4857</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177887</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45504</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2754762</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>7915</v>
+        <v>2202</v>
       </c>
       <c r="F8" t="n">
-        <v>23008</v>
+        <v>6669</v>
       </c>
       <c r="G8" t="n">
-        <v>9064</v>
+        <v>3130</v>
       </c>
       <c r="H8" t="n">
-        <v>244034</v>
+        <v>66445</v>
       </c>
       <c r="I8" t="n">
-        <v>875744</v>
+        <v>114927</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
